--- a/UMD semantically-expanded test texts.xlsx
+++ b/UMD semantically-expanded test texts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\OpenDI-release\repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A48F9B1-62FC-46D1-9403-550887798BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CB809F-6B7C-4B36-8436-4AC21705C7EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15360" yWindow="0" windowWidth="15360" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test texts" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="154">
   <si>
     <t>Object</t>
   </si>
@@ -61,424 +61,432 @@
     <t>Saw</t>
   </si>
   <si>
+    <t>Cut with the saw</t>
+  </si>
+  <si>
+    <t>Saw through the piece of wood</t>
+  </si>
+  <si>
+    <t>Carefully saw through the wood with steady backstrokes</t>
+  </si>
+  <si>
+    <t>Scissors</t>
+  </si>
+  <si>
+    <t>Snip apart</t>
+  </si>
+  <si>
+    <t>Cut with the scissors</t>
+  </si>
+  <si>
+    <t>Cut the paper using the scissors</t>
+  </si>
+  <si>
+    <t>Carefully cut along the paper using the scissors</t>
+  </si>
+  <si>
+    <t>Shears</t>
+  </si>
+  <si>
+    <t>Trim by cutting</t>
+  </si>
+  <si>
+    <t>Cut with the shears</t>
+  </si>
+  <si>
+    <t>Trim the branches using the shears</t>
+  </si>
+  <si>
+    <t>Carefully trim the small branches using the sharp shears</t>
+  </si>
+  <si>
+    <t>Scoop</t>
+  </si>
+  <si>
+    <t>Scoop up</t>
+  </si>
+  <si>
+    <t>Scoop with the scoop</t>
+  </si>
+  <si>
+    <t>Scoop up flour using the scoop</t>
+  </si>
+  <si>
+    <t>Gently scoop up some flour using the scoop</t>
+  </si>
+  <si>
+    <t>Spoon</t>
+  </si>
+  <si>
+    <t>Spoon up</t>
+  </si>
+  <si>
+    <t>Scoop with the spoon</t>
+  </si>
+  <si>
+    <t>Scoop up food using the spoon</t>
+  </si>
+  <si>
+    <t>Carefully scoop up some food using the spoon</t>
+  </si>
+  <si>
+    <t>Trowel</t>
+  </si>
+  <si>
+    <t>Scoop out</t>
+  </si>
+  <si>
+    <t>Scoop with the trowel</t>
+  </si>
+  <si>
+    <t>Scoop the material with the trowel</t>
+  </si>
+  <si>
+    <t>Carefully scoop some loose soil out using the trowel</t>
+  </si>
+  <si>
+    <t>Bowl</t>
+  </si>
+  <si>
+    <t>Contain</t>
+  </si>
+  <si>
+    <t>Keep inside</t>
+  </si>
+  <si>
+    <t>Contain in the bowl</t>
+  </si>
+  <si>
+    <t>Keep the food inside the bowl</t>
+  </si>
+  <si>
+    <t>Cup</t>
+  </si>
+  <si>
+    <t>Retain liquid</t>
+  </si>
+  <si>
+    <t>Contain in the cup</t>
+  </si>
+  <si>
+    <t>Fill the container with water</t>
+  </si>
+  <si>
+    <t>Ladle</t>
+  </si>
+  <si>
+    <t>Retain contents</t>
+  </si>
+  <si>
+    <t>Contain in the ladle</t>
+  </si>
+  <si>
+    <t>Keep the soup inside the ladle</t>
+  </si>
+  <si>
+    <t>Mug</t>
+  </si>
+  <si>
+    <t>Keep liquid inside</t>
+  </si>
+  <si>
+    <t>Contain in the mug</t>
+  </si>
+  <si>
+    <t>Keep the drink inside the mug</t>
+  </si>
+  <si>
+    <t>Keep the drink contained inside the mug without spilling</t>
+  </si>
+  <si>
+    <t>Pot</t>
+  </si>
+  <si>
+    <t>Contain in the pot</t>
+  </si>
+  <si>
+    <t>Keep the soup inside the pot</t>
+  </si>
+  <si>
+    <t>Keep the soup contained inside the pot without spilling</t>
+  </si>
+  <si>
+    <t>Shovel</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>Support from below</t>
+  </si>
+  <si>
+    <t>Support with the shovel</t>
+  </si>
+  <si>
+    <t>Support the soil on the shovel</t>
+  </si>
+  <si>
+    <t>Keep the soil supported on the shovel from below</t>
+  </si>
+  <si>
+    <t>Turner</t>
+  </si>
+  <si>
+    <t>Bear weight</t>
+  </si>
+  <si>
+    <t>Support with the turner</t>
+  </si>
+  <si>
+    <t>Support the food on the turner</t>
+  </si>
+  <si>
+    <t>Keep the food supported on the turner from below</t>
+  </si>
+  <si>
+    <t>Hammer</t>
+  </si>
+  <si>
+    <t>Pound</t>
+  </si>
+  <si>
+    <t>Strike repeatedly</t>
+  </si>
+  <si>
+    <t>Pound with the hammer</t>
+  </si>
+  <si>
+    <t>Pound the surface with the hammer</t>
+  </si>
+  <si>
+    <t>Repeatedly pound the surface using the hammer with control</t>
+  </si>
+  <si>
+    <t>Mallet</t>
+  </si>
+  <si>
+    <t>Deliver repeated blows</t>
+  </si>
+  <si>
+    <t>Pound with the mallet</t>
+  </si>
+  <si>
+    <t>Pound the surface with the mallet</t>
+  </si>
+  <si>
+    <t>Repeatedly pound the surface using the mallet with control</t>
+  </si>
+  <si>
+    <t>Tenderizer</t>
+  </si>
+  <si>
+    <t>Pound repeatedly</t>
+  </si>
+  <si>
+    <t>Pound with the tenderizer</t>
+  </si>
+  <si>
+    <t>Pound the meat using the tenderizer</t>
+  </si>
+  <si>
+    <t>Apply even strikes across the meat surface</t>
+  </si>
+  <si>
+    <t>Wrap-grasp</t>
+  </si>
+  <si>
+    <t>Grasp the cup</t>
+  </si>
+  <si>
+    <t>Wrap your hand around the cup</t>
+  </si>
+  <si>
+    <t>Grasp the cup by wrapping your hand around</t>
+  </si>
+  <si>
+    <t>Firmly grasp the cup by wrapping your hand around</t>
+  </si>
+  <si>
+    <t>Grasp</t>
+  </si>
+  <si>
+    <t>Take hold</t>
+  </si>
+  <si>
+    <t>Grasp the hammer</t>
+  </si>
+  <si>
+    <t>Grasp the hammer with a firm grip</t>
+  </si>
+  <si>
+    <t>Securely grasp the hammer and keep your grip steady</t>
+  </si>
+  <si>
+    <t>Grasp the knife</t>
+  </si>
+  <si>
+    <t>Grasp the knife with a firm grip</t>
+  </si>
+  <si>
+    <t>Securely grasp the knife and keep your grip steady</t>
+  </si>
+  <si>
+    <t>Grasp the ladle</t>
+  </si>
+  <si>
+    <t>Grasp the ladle with a firm grip</t>
+  </si>
+  <si>
+    <t>Securely grasp the ladle and keep your grip steady</t>
+  </si>
+  <si>
+    <t>Grasp the mallet</t>
+  </si>
+  <si>
+    <t>Grasp the mallet with a firm grip</t>
+  </si>
+  <si>
+    <t>Securely grasp the mallet and keep your grip steady</t>
+  </si>
+  <si>
+    <t>Grasp the mug</t>
+  </si>
+  <si>
+    <t>Grasp the mug with a firm grip</t>
+  </si>
+  <si>
+    <t>Securely grasp the mug and keep your grip steady</t>
+  </si>
+  <si>
+    <t>Grip by encircling</t>
+  </si>
+  <si>
+    <t>Wrap your hand around the mug</t>
+  </si>
+  <si>
+    <t>Grasp the mug by wrapping your hand around</t>
+  </si>
+  <si>
+    <t>Firmly grasp the mug by wrapping your hand around</t>
+  </si>
+  <si>
+    <t>Grasp the pot</t>
+  </si>
+  <si>
+    <t>Grasp the pot with a firm grip</t>
+  </si>
+  <si>
+    <t>Securely grasp the pot and keep your grip steady</t>
+  </si>
+  <si>
+    <t>Wrap your hand around the pot</t>
+  </si>
+  <si>
+    <t>Grasp the pot by wrapping your hand around</t>
+  </si>
+  <si>
+    <t>Firmly grasp the pot by wrapping your hand around</t>
+  </si>
+  <si>
+    <t>Grasp the saw</t>
+  </si>
+  <si>
+    <t>Grasp the saw with a firm grip</t>
+  </si>
+  <si>
+    <t>Securely grasp the saw and keep your grip steady</t>
+  </si>
+  <si>
+    <t>Grasp the scissors</t>
+  </si>
+  <si>
+    <t>Grasp the scissors with a firm grip</t>
+  </si>
+  <si>
+    <t>Securely grasp the scissors and keep your grip steady</t>
+  </si>
+  <si>
+    <t>Grasp the scoop</t>
+  </si>
+  <si>
+    <t>Grasp the scoop with a firm grip</t>
+  </si>
+  <si>
+    <t>Securely grasp the scoop and keep your grip steady</t>
+  </si>
+  <si>
+    <t>Grasp the shears</t>
+  </si>
+  <si>
+    <t>Grasp the shears with a firm grip</t>
+  </si>
+  <si>
+    <t>Securely grasp the shears and keep your grip steady</t>
+  </si>
+  <si>
+    <t>Grasp the shovel</t>
+  </si>
+  <si>
+    <t>Grasp the shovel with a firm grip</t>
+  </si>
+  <si>
+    <t>Securely grasp the shovel and keep your grip steady</t>
+  </si>
+  <si>
+    <t>Grasp the spoon</t>
+  </si>
+  <si>
+    <t>Grasp the spoon with a firm grip</t>
+  </si>
+  <si>
+    <t>Securely grasp the spoon and keep your grip steady</t>
+  </si>
+  <si>
+    <t>Catch hold of the meat tenderizer</t>
+  </si>
+  <si>
+    <t>Grasp the tenderizer with a firm grip</t>
+  </si>
+  <si>
+    <t>Grasp the trowel</t>
+  </si>
+  <si>
+    <t>Catch hold of the trowel</t>
+  </si>
+  <si>
+    <t>Securely grasp the trowel and keep your grip steady</t>
+  </si>
+  <si>
+    <t>Grasp the turner</t>
+  </si>
+  <si>
+    <t>Grasp the turner with a firm grip</t>
+  </si>
+  <si>
+    <t>Securely grasp the turner and keep your grip steady</t>
+  </si>
+  <si>
+    <t>Contain the liquid securely inside the ladle</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>Saw through</t>
-  </si>
-  <si>
-    <t>Cut with the saw</t>
-  </si>
-  <si>
-    <t>Saw through the piece of wood</t>
-  </si>
-  <si>
-    <t>Carefully saw through the wood with steady backstrokes</t>
-  </si>
-  <si>
-    <t>Scissors</t>
-  </si>
-  <si>
-    <t>Snip apart</t>
-  </si>
-  <si>
-    <t>Cut with the scissors</t>
-  </si>
-  <si>
-    <t>Cut the paper using the scissors</t>
-  </si>
-  <si>
-    <t>Carefully cut along the paper using the scissors</t>
-  </si>
-  <si>
-    <t>Shears</t>
-  </si>
-  <si>
-    <t>Trim by cutting</t>
-  </si>
-  <si>
-    <t>Cut with the shears</t>
-  </si>
-  <si>
-    <t>Trim the branches using the shears</t>
-  </si>
-  <si>
-    <t>Carefully trim the small branches using the sharp shears</t>
-  </si>
-  <si>
-    <t>Scoop</t>
-  </si>
-  <si>
-    <t>Scoop up</t>
-  </si>
-  <si>
-    <t>Scoop with the scoop</t>
-  </si>
-  <si>
-    <t>Scoop up flour using the scoop</t>
-  </si>
-  <si>
-    <t>Gently scoop up some flour using the scoop</t>
-  </si>
-  <si>
-    <t>Spoon</t>
-  </si>
-  <si>
-    <t>Spoon up</t>
-  </si>
-  <si>
-    <t>Scoop with the spoon</t>
-  </si>
-  <si>
-    <t>Scoop up food using the spoon</t>
-  </si>
-  <si>
-    <t>Carefully scoop up some food using the spoon</t>
-  </si>
-  <si>
-    <t>Trowel</t>
-  </si>
-  <si>
-    <t>Scoop out</t>
-  </si>
-  <si>
-    <t>Scoop with the trowel</t>
-  </si>
-  <si>
-    <t>Scoop the material with the trowel</t>
-  </si>
-  <si>
-    <t>Carefully scoop some loose soil out using the trowel</t>
-  </si>
-  <si>
-    <t>Bowl</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Contain</t>
-  </si>
-  <si>
-    <t>Keep inside</t>
-  </si>
-  <si>
-    <t>Contain in the bowl</t>
-  </si>
-  <si>
-    <t>Keep the food inside the bowl</t>
-  </si>
-  <si>
-    <t>Keep the food contained inside the bowl without spilling</t>
-  </si>
-  <si>
-    <t>Cup</t>
-  </si>
-  <si>
-    <t>Retain liquid</t>
-  </si>
-  <si>
-    <t>Contain in the cup</t>
-  </si>
-  <si>
-    <t>Fill the container with water</t>
-  </si>
-  <si>
-    <t>Keep the water contained inside the cup without spilling</t>
-  </si>
-  <si>
-    <t>Ladle</t>
-  </si>
-  <si>
-    <t>Retain contents</t>
-  </si>
-  <si>
-    <t>Contain in the ladle</t>
-  </si>
-  <si>
-    <t>Keep the soup inside the ladle</t>
-  </si>
-  <si>
-    <t>Mug</t>
-  </si>
-  <si>
-    <t>Keep liquid inside</t>
-  </si>
-  <si>
-    <t>Contain in the mug</t>
-  </si>
-  <si>
-    <t>Keep the drink inside the mug</t>
-  </si>
-  <si>
-    <t>Keep the drink contained inside the mug without spilling</t>
-  </si>
-  <si>
-    <t>Pot</t>
-  </si>
-  <si>
-    <t>Contain in the pot</t>
-  </si>
-  <si>
-    <t>Keep the soup inside the pot</t>
-  </si>
-  <si>
-    <t>Keep the soup contained inside the pot without spilling</t>
-  </si>
-  <si>
-    <t>Shovel</t>
-  </si>
-  <si>
-    <t>Support</t>
-  </si>
-  <si>
-    <t>Support from below</t>
-  </si>
-  <si>
-    <t>Support with the shovel</t>
-  </si>
-  <si>
-    <t>Support the soil on the shovel</t>
-  </si>
-  <si>
-    <t>Keep the soil supported on the shovel from below</t>
-  </si>
-  <si>
-    <t>Turner</t>
-  </si>
-  <si>
-    <t>Bear weight</t>
-  </si>
-  <si>
-    <t>Support with the turner</t>
-  </si>
-  <si>
-    <t>Support the food on the turner</t>
-  </si>
-  <si>
-    <t>Keep the food supported on the turner from below</t>
-  </si>
-  <si>
-    <t>Hammer</t>
-  </si>
-  <si>
-    <t>Pound</t>
-  </si>
-  <si>
-    <t>Strike repeatedly</t>
-  </si>
-  <si>
-    <t>Pound with the hammer</t>
-  </si>
-  <si>
-    <t>Pound the surface with the hammer</t>
-  </si>
-  <si>
-    <t>Repeatedly pound the surface using the hammer with control</t>
-  </si>
-  <si>
-    <t>Mallet</t>
-  </si>
-  <si>
-    <t>Deliver repeated blows</t>
-  </si>
-  <si>
-    <t>Pound with the mallet</t>
-  </si>
-  <si>
-    <t>Pound the surface with the mallet</t>
-  </si>
-  <si>
-    <t>Repeatedly pound the surface using the mallet with control</t>
-  </si>
-  <si>
-    <t>Tenderizer</t>
-  </si>
-  <si>
-    <t>Pound repeatedly</t>
-  </si>
-  <si>
-    <t>Pound with the tenderizer</t>
-  </si>
-  <si>
-    <t>Pound the meat using the tenderizer</t>
-  </si>
-  <si>
-    <t>Apply even strikes across the meat surface</t>
-  </si>
-  <si>
-    <t>Wrap-grasp</t>
-  </si>
-  <si>
-    <t>Grasp the cup</t>
-  </si>
-  <si>
-    <t>Wrap your hand around the cup</t>
-  </si>
-  <si>
-    <t>Grasp the cup by wrapping your hand around</t>
-  </si>
-  <si>
-    <t>Firmly grasp the cup by wrapping your hand around</t>
-  </si>
-  <si>
-    <t>Grasp</t>
-  </si>
-  <si>
-    <t>Take hold</t>
-  </si>
-  <si>
-    <t>Grasp the hammer</t>
-  </si>
-  <si>
-    <t>Grasp the hammer with a firm grip</t>
-  </si>
-  <si>
-    <t>Securely grasp the hammer and keep your grip steady</t>
-  </si>
-  <si>
-    <t>Grasp the knife</t>
-  </si>
-  <si>
-    <t>Grasp the knife with a firm grip</t>
-  </si>
-  <si>
-    <t>Securely grasp the knife and keep your grip steady</t>
-  </si>
-  <si>
-    <t>Grasp the ladle</t>
-  </si>
-  <si>
-    <t>Grasp the ladle with a firm grip</t>
-  </si>
-  <si>
-    <t>Securely grasp the ladle and keep your grip steady</t>
-  </si>
-  <si>
-    <t>Grasp the mallet</t>
-  </si>
-  <si>
-    <t>Grasp the mallet with a firm grip</t>
-  </si>
-  <si>
-    <t>Securely grasp the mallet and keep your grip steady</t>
-  </si>
-  <si>
-    <t>Grasp the mug</t>
-  </si>
-  <si>
-    <t>Grasp the mug with a firm grip</t>
-  </si>
-  <si>
-    <t>Securely grasp the mug and keep your grip steady</t>
-  </si>
-  <si>
-    <t>Grip by encircling</t>
-  </si>
-  <si>
-    <t>Wrap your hand around the mug</t>
-  </si>
-  <si>
-    <t>Grasp the mug by wrapping your hand around</t>
-  </si>
-  <si>
-    <t>Firmly grasp the mug by wrapping your hand around</t>
-  </si>
-  <si>
-    <t>Grasp the pot</t>
-  </si>
-  <si>
-    <t>Grasp the pot with a firm grip</t>
-  </si>
-  <si>
-    <t>Securely grasp the pot and keep your grip steady</t>
-  </si>
-  <si>
-    <t>Wrap your hand around the pot</t>
-  </si>
-  <si>
-    <t>Grasp the pot by wrapping your hand around</t>
-  </si>
-  <si>
-    <t>Firmly grasp the pot by wrapping your hand around</t>
-  </si>
-  <si>
-    <t>Grasp the saw</t>
-  </si>
-  <si>
-    <t>Grasp the saw with a firm grip</t>
-  </si>
-  <si>
-    <t>Securely grasp the saw and keep your grip steady</t>
-  </si>
-  <si>
-    <t>Grasp the scissors</t>
-  </si>
-  <si>
-    <t>Grasp the scissors with a firm grip</t>
-  </si>
-  <si>
-    <t>Securely grasp the scissors and keep your grip steady</t>
-  </si>
-  <si>
-    <t>Grasp the scoop</t>
-  </si>
-  <si>
-    <t>Grasp the scoop with a firm grip</t>
-  </si>
-  <si>
-    <t>Securely grasp the scoop and keep your grip steady</t>
-  </si>
-  <si>
-    <t>Grasp the shears</t>
-  </si>
-  <si>
-    <t>Grasp the shears with a firm grip</t>
-  </si>
-  <si>
-    <t>Securely grasp the shears and keep your grip steady</t>
-  </si>
-  <si>
-    <t>Grasp the shovel</t>
-  </si>
-  <si>
-    <t>Grasp the shovel with a firm grip</t>
-  </si>
-  <si>
-    <t>Securely grasp the shovel and keep your grip steady</t>
-  </si>
-  <si>
-    <t>Grasp the spoon</t>
-  </si>
-  <si>
-    <t>Grasp the spoon with a firm grip</t>
-  </si>
-  <si>
-    <t>Securely grasp the spoon and keep your grip steady</t>
-  </si>
-  <si>
-    <t>Catch hold of the meat tenderizer</t>
-  </si>
-  <si>
-    <t>Grasp the tenderizer with a firm grip</t>
-  </si>
-  <si>
-    <t>Lower the tenderizer carefully onto the designated surface</t>
-  </si>
-  <si>
-    <t>Grasp the trowel</t>
-  </si>
-  <si>
-    <t>Catch hold of the trowel</t>
-  </si>
-  <si>
-    <t>Securely grasp the trowel and keep your grip steady</t>
-  </si>
-  <si>
-    <t>Grasp the turner</t>
-  </si>
-  <si>
-    <t>Grasp the turner with a firm grip</t>
-  </si>
-  <si>
-    <t>Securely grasp the turner and keep your grip steady</t>
-  </si>
-  <si>
-    <t>Contain the liquid securely inside the ladle</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Keep the food contained inside the bowl</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Keep the water contained inside the cup</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grasp the tenderizer carefully onto the designated surface</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -825,356 +833,356 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="52.05" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="52.05" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="52.05" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="52.05" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="52.05" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="52.05" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>47</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="52.05" customHeight="1">
       <c r="A10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>52</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="52.05" customHeight="1">
       <c r="A11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="52.05" customHeight="1">
       <c r="A12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="52.05" customHeight="1">
       <c r="A13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="52.05" customHeight="1">
       <c r="A14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="52.05" customHeight="1">
       <c r="A15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="52.05" customHeight="1">
       <c r="A16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="52.05" customHeight="1">
       <c r="A17" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="52.05" customHeight="1">
       <c r="A18" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="52.05" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="52.05" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="52.05" customHeight="1">
@@ -1182,139 +1190,139 @@
         <v>6</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="52.05" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="52.05" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="52.05" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="52.05" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="52.05" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="52.05" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="52.05" customHeight="1">
@@ -1322,179 +1330,179 @@
         <v>12</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="52.05" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="52.05" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="52.05" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="52.05" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="52.05" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="52.05" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="52.05" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="52.05" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
